--- a/outputs/142-12.xlsx
+++ b/outputs/142-12.xlsx
@@ -134,32 +134,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -415,324 +419,324 @@
   <dimension ref="C1:J15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="33.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="n">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="n">
         <v>44915</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="2" t="n">
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="3" t="n">
         <v>-12.81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="n">
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>44922</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2" t="n">
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>-13.22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="n">
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>44929</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="2" t="n">
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>-8.9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="C4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>44900</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="5" t="n">
+      <c r="F4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="6" t="n">
         <v>-470.64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="C5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>44929</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="5" t="n">
+      <c r="F5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="6" t="n">
         <v>-39.95</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3" t="n">
+      <c r="C6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>44900</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="5" t="n">
+      <c r="F6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6" t="n">
         <v>-58.45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3" t="n">
+      <c r="C7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>44929</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5" t="n">
+      <c r="F7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6" t="n">
         <v>-54.3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="n">
+      <c r="C8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>44900</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="5" t="n">
+      <c r="F8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6" t="n">
         <v>-273.55</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="n">
+      <c r="C9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>44897</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="5" t="n">
+      <c r="F9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="6" t="n">
         <v>-106.87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="n">
+      <c r="C10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>44936</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="5" t="n">
+      <c r="G10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="6" t="n">
         <v>-507</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="n">
+      <c r="C11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>44929</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2" t="n">
+      <c r="F11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="3" t="n">
         <v>-421.72</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="n">
+      <c r="C12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>44929</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="2" t="n">
+      <c r="F12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>-238.17</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="n">
+      <c r="C13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>44907</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="2" t="n">
+      <c r="G13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="3" t="n">
         <v>-572</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="n">
+      <c r="C14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>44929</v>
       </c>
-      <c r="F14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="2" t="n">
+      <c r="F14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>-255.87</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="n">
+      <c r="C15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>44936</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="2" t="n">
+      <c r="G15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="n">
         <v>-32.94</v>
       </c>
     </row>

--- a/outputs/142-12.xlsx
+++ b/outputs/142-12.xlsx
@@ -651,7 +651,7 @@
         <v>44929</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>3</v>
@@ -671,7 +671,7 @@
         <v>44929</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>3</v>
